--- a/ejemplo/maestro_ejemplo.xlsx
+++ b/ejemplo/maestro_ejemplo.xlsx
@@ -143,7 +143,104 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tblLabor" displayName="tblLabor" ref="AM1:AW7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tblUser" displayName="tblUser" ref="F1:G4" headerRowCount="1">
+  <autoFilter ref="F1:G4"/>
+  <tableColumns count="2">
+    <tableColumn id="6" name="User / 用户"/>
+    <tableColumn id="7" name="Code / 代码"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tblRequester" displayName="tblRequester" ref="M1:N4" headerRowCount="1">
+  <autoFilter ref="M1:N4"/>
+  <tableColumns count="2">
+    <tableColumn id="13" name="Requester / 申请人"/>
+    <tableColumn id="14" name="Code / 代码"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tblProfile" displayName="tblProfile" ref="T1:T4" headerRowCount="1">
+  <autoFilter ref="T1:T4"/>
+  <tableColumns count="1">
+    <tableColumn id="20" name="Profile / 用户档案"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblShift" displayName="tblShift" ref="I1:K3" headerRowCount="1">
+  <autoFilter ref="I1:K3"/>
+  <tableColumns count="3">
+    <tableColumn id="9" name="Shift / 班"/>
+    <tableColumn id="10" name="Start / 开始"/>
+    <tableColumn id="11" name="End / 结束"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblMachineStatus" displayName="tblMachineStatus" ref="P1:P7" headerRowCount="1">
+  <autoFilter ref="P1:P7"/>
+  <tableColumns count="1">
+    <tableColumn id="16" name="Machine Status / 设备状态"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblMachineType" displayName="tblMachineType" ref="R1:R5" headerRowCount="1">
+  <autoFilter ref="R1:R5"/>
+  <tableColumns count="1">
+    <tableColumn id="18" name="Type / 类型"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblOperator" displayName="tblOperator" ref="V1:AB11" headerRowCount="1">
+  <autoFilter ref="V1:AB11"/>
+  <tableColumns count="7">
+    <tableColumn id="22" name="Operator name / 操作员名称"/>
+    <tableColumn id="23" name="Code / 代码"/>
+    <tableColumn id="24" name="Range / 范围"/>
+    <tableColumn id="25" name="Range / 范围2"/>
+    <tableColumn id="26" name="Contractor / 承包商"/>
+    <tableColumn id="27" name="Guard / 警卫"/>
+    <tableColumn id="28" name="Active / 积极的"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tblMachine" displayName="tblMachine" ref="AD1:AK7" headerRowCount="1">
+  <autoFilter ref="AD1:AK7"/>
+  <tableColumns count="8">
+    <tableColumn id="30" name="Machine name / 机器名称"/>
+    <tableColumn id="31" name="Machine Code / 机器码"/>
+    <tableColumn id="32" name="Type / 类型"/>
+    <tableColumn id="33" name="Contractor / 承包商"/>
+    <tableColumn id="34" name="Capacity [m³] / 容量"/>
+    <tableColumn id="35" name="Status / 状态"/>
+    <tableColumn id="36" name="Observation / 备注"/>
+    <tableColumn id="37" name="Active / 积极的"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblLabor" displayName="tblLabor" ref="AM1:AW7" headerRowCount="1">
   <autoFilter ref="AM1:AW7"/>
   <tableColumns count="11">
     <tableColumn id="39" name="Month / 月"/>
@@ -162,8 +259,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tblMezcla" displayName="tblMezcla" ref="AY1:AZ11" headerRowCount="1">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblMezcla" displayName="tblMezcla" ref="AY1:AZ11" headerRowCount="1">
   <autoFilter ref="AY1:AZ11"/>
   <tableColumns count="2">
     <tableColumn id="51" name="Mezcla / 混合料"/>
@@ -173,108 +270,11 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tblCategoriaM" displayName="tblCategoriaM" ref="BB1:BB7" headerRowCount="1">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tblCategoriaM" displayName="tblCategoriaM" ref="BB1:BB7" headerRowCount="1">
   <autoFilter ref="BB1:BB7"/>
   <tableColumns count="1">
     <tableColumn id="54" name="Categoria M / 类别"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblContractor" displayName="tblContractor" ref="F1:G4" headerRowCount="1">
-  <autoFilter ref="F1:G4"/>
-  <tableColumns count="2">
-    <tableColumn id="6" name="Contractor / 承包商"/>
-    <tableColumn id="7" name="Code / 代码"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblShift" displayName="tblShift" ref="I1:K3" headerRowCount="1">
-  <autoFilter ref="I1:K3"/>
-  <tableColumns count="3">
-    <tableColumn id="9" name="Shift / 班"/>
-    <tableColumn id="10" name="Start / 开始"/>
-    <tableColumn id="11" name="End / 结束"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblGerencia" displayName="tblGerencia" ref="M1:N4" headerRowCount="1">
-  <autoFilter ref="M1:N4"/>
-  <tableColumns count="2">
-    <tableColumn id="13" name="Gerencia / 管理层"/>
-    <tableColumn id="14" name="Code / 代码"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblMachineStatus" displayName="tblMachineStatus" ref="P1:P7" headerRowCount="1">
-  <autoFilter ref="P1:P7"/>
-  <tableColumns count="1">
-    <tableColumn id="16" name="Status / 状态"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tblMachineType" displayName="tblMachineType" ref="R1:R5" headerRowCount="1">
-  <autoFilter ref="R1:R5"/>
-  <tableColumns count="1">
-    <tableColumn id="18" name="Type / 类型"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblRange" displayName="tblRange" ref="T1:T4" headerRowCount="1">
-  <autoFilter ref="T1:T4"/>
-  <tableColumns count="1">
-    <tableColumn id="20" name="Range / 范围"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblOperator" displayName="tblOperator" ref="V1:AB11" headerRowCount="1">
-  <autoFilter ref="V1:AB11"/>
-  <tableColumns count="7">
-    <tableColumn id="22" name="Operator name / 操作员名称"/>
-    <tableColumn id="23" name="Code / 代码"/>
-    <tableColumn id="24" name="Range / 范围"/>
-    <tableColumn id="25" name="Range / 范围2"/>
-    <tableColumn id="26" name="Contractor / 承包商"/>
-    <tableColumn id="27" name="Guard / 警卫"/>
-    <tableColumn id="28" name="Active / 积极的"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tblMachine" displayName="tblMachine" ref="AD1:AK7" headerRowCount="1">
-  <autoFilter ref="AD1:AK7"/>
-  <tableColumns count="8">
-    <tableColumn id="30" name="Machine name / 机器名称"/>
-    <tableColumn id="31" name="Machine Code / 机器码"/>
-    <tableColumn id="32" name="Type / 类型"/>
-    <tableColumn id="33" name="Contractor / 承包商"/>
-    <tableColumn id="34" name="Capacity [m³] / 容量"/>
-    <tableColumn id="35" name="Status / 状态"/>
-    <tableColumn id="36" name="Observation / 备注"/>
-    <tableColumn id="37" name="Active / 积极的"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -640,7 +640,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Contractor / 承包商</t>
+          <t>User / 用户</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Gerencia / 管理层</t>
+          <t>Requester / 申请人</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Status / 状态</t>
+          <t>Machine Status / 设备状态</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Range / 范围</t>
+          <t>Profile / 用户档案</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
